--- a/Manual/source/tab/parametersEN.xlsx
+++ b/Manual/source/tab/parametersEN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="293">
   <si>
     <t xml:space="preserve">POWER SUPPLY</t>
   </si>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">24 VDC ± 10 %, 600 mA*</t>
   </si>
   <si>
-    <t xml:space="preserve">0-320 VDC (pojistka 10 A)</t>
+    <t xml:space="preserve">0-320 VDC (fuse 10 A)</t>
   </si>
   <si>
     <t xml:space="preserve">2,6 kW</t>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t xml:space="preserve">2 x 10 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED signaling (axis 1 and 2 separately)</t>
   </si>
   <si>
     <t xml:space="preserve">1 x 3pin PHOENIX  PC 5/ 3-STCL1-7,62  </t>
@@ -1754,7 +1757,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>32</v>
@@ -1773,7 +1776,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1789,7 +1792,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1852,7 +1855,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1969,7 +1972,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>32</v>
@@ -1988,7 +1991,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2004,7 +2007,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2067,7 +2070,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2075,7 +2078,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2083,7 +2086,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2091,7 +2094,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2104,10 +2107,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2219,7 +2222,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2235,7 +2238,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2260,7 +2263,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B30" s="3"/>
     </row>
@@ -2269,7 +2272,7 @@
         <v>117</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2316,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2324,7 +2327,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2332,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2353,10 +2356,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2468,7 +2471,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2484,7 +2487,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2509,7 +2512,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B30" s="3"/>
     </row>
@@ -2518,7 +2521,7 @@
         <v>117</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2565,7 +2568,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2573,7 +2576,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2581,7 +2584,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2589,7 +2592,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2602,10 +2605,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2717,7 +2720,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2733,7 +2736,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2758,7 +2761,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B30" s="3"/>
     </row>
@@ -2767,7 +2770,7 @@
         <v>117</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2814,7 +2817,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2822,7 +2825,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2830,7 +2833,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2838,7 +2841,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2846,15 +2849,15 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2966,7 +2969,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2982,7 +2985,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3007,7 +3010,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B30" s="3"/>
     </row>
@@ -3016,7 +3019,7 @@
         <v>117</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3055,7 +3058,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3063,7 +3066,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3071,7 +3074,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3079,7 +3082,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3087,7 +3090,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3103,7 +3106,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3199,7 +3202,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3207,7 +3210,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3223,7 +3226,7 @@
         <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3231,7 +3234,7 @@
         <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3239,12 +3242,12 @@
         <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3252,7 +3255,7 @@
         <v>117</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -3289,91 +3292,91 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -3388,7 +3391,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -3396,18 +3399,18 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3423,12 +3426,12 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1</v>
@@ -3436,26 +3439,26 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3492,16 +3495,16 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -3510,25 +3513,25 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>46</v>
@@ -3537,25 +3540,25 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -3564,19 +3567,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -3591,7 +3594,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -3599,18 +3602,18 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3626,12 +3629,12 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1</v>
@@ -3642,12 +3645,12 @@
         <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>1</v>
@@ -3655,7 +3658,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>1</v>
@@ -3663,10 +3666,10 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3929,21 +3932,21 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>46</v>
@@ -3952,16 +3955,16 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>46</v>
@@ -3970,7 +3973,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>56</v>
@@ -3979,25 +3982,25 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
@@ -4006,19 +4009,19 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -4033,7 +4036,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -4041,18 +4044,18 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4068,12 +4071,12 @@
         <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>1</v>
@@ -4084,47 +4087,47 @@
         <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -4161,28 +4164,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -4200,19 +4203,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -4227,28 +4230,28 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -4266,16 +4269,16 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1</v>
@@ -4283,10 +4286,10 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4294,15 +4297,15 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4339,28 +4342,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -4405,10 +4408,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -4426,10 +4429,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -4438,7 +4441,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -4447,7 +4450,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>37</v>
@@ -4458,7 +4461,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4519,28 +4522,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -4585,10 +4588,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -4606,10 +4609,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -4618,7 +4621,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -4630,7 +4633,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4657,7 +4660,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
@@ -4673,107 +4676,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="K1" s="0" t="s">
         <v>245</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4781,16 +4784,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2.05</v>
@@ -4816,16 +4819,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2.05</v>
@@ -4851,16 +4854,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2.05</v>
@@ -4886,16 +4889,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2.05</v>
@@ -4921,16 +4924,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2.05</v>
@@ -4956,16 +4959,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2.05</v>
@@ -4991,16 +4994,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1.25</v>
@@ -5026,16 +5029,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1.25</v>
@@ -5055,18 +5058,6 @@
       <c r="K11" s="1" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0"/>
-      <c r="C19" s="0"/>
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0"/>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0"/>
-      <c r="K19" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5084,7 +5075,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
@@ -5099,89 +5090,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="I1" s="0" t="s">
         <v>276</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5201,7 +5192,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>300</v>
@@ -5230,7 +5221,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>300</v>
@@ -5259,7 +5250,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>300</v>
@@ -5288,7 +5279,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>300</v>
@@ -5317,7 +5308,7 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>300</v>
@@ -5346,7 +5337,7 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>300</v>
@@ -5357,16 +5348,6 @@
       <c r="I9" s="1" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0"/>
-      <c r="C19" s="0"/>
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0"/>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-      <c r="I19" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5384,7 +5365,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
@@ -5395,44 +5376,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D1" s="0" t="s">
         <v>287</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5440,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>11</v>
@@ -5454,7 +5435,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>11</v>
@@ -5462,11 +5443,6 @@
       <c r="D5" s="1" t="n">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0"/>
-      <c r="C13" s="0"/>
-      <c r="D13" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/tab/parametersEN.xlsx
+++ b/Manual/source/tab/parametersEN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,25 +15,28 @@
     <sheet name="TGZ-S-48-100_250RI" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="TGZ-S-48-100_300RI" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="TGZ-S-48-100_250" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="TGZ-S-48-100_300" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="TGZ-S-48-100_425" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="TGZ-S-230-5_15" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="TGZ-D-320-5_10" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="TGZ-D-320-5_15" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="TGZ-S-400-3_9" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="TGZ-S-400-7_15" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="TGZ-S-400-10_20" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="TGZ-S-400-14_30" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="TGZ-D-560-30_50" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="TGS-320-10_15" sheetId="18" state="visible" r:id="rId20"/>
-    <sheet name="TGS-560-25_50" sheetId="19" state="visible" r:id="rId21"/>
-    <sheet name="TGS-560-50_100" sheetId="20" state="visible" r:id="rId22"/>
-    <sheet name="TGMmini" sheetId="21" state="visible" r:id="rId23"/>
-    <sheet name="TGMcontroller" sheetId="22" state="visible" r:id="rId24"/>
-    <sheet name="TGZpMotion" sheetId="23" state="visible" r:id="rId25"/>
-    <sheet name="commonHW_DI" sheetId="24" state="visible" r:id="rId26"/>
-    <sheet name="commonHW_DO" sheetId="25" state="visible" r:id="rId27"/>
-    <sheet name="commonHW_AI" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="TGZ-S-48-100_250-O" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="TGZ-S-48-100_300" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="TGZ-S-48-100_300-O" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="TGZ-S-48-100_425" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="TGZ-S-48-100_425-O" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="TGZ-S-230-5_15" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="TGZ-D-320-5_10" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="TGZ-D-320-5_15" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="TGZ-S-400-3_9" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="TGZ-S-400-7_15" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="TGZ-S-400-10_20" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="TGZ-S-400-14_30" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="TGZ-D-560-30_50" sheetId="20" state="visible" r:id="rId22"/>
+    <sheet name="TGS-320-10_15" sheetId="21" state="visible" r:id="rId23"/>
+    <sheet name="TGS-560-25_50" sheetId="22" state="visible" r:id="rId24"/>
+    <sheet name="TGS-560-50_100" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="TGMmini" sheetId="24" state="visible" r:id="rId26"/>
+    <sheet name="TGMcontroller" sheetId="25" state="visible" r:id="rId27"/>
+    <sheet name="TGZpMotion" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="commonHW_DI" sheetId="27" state="visible" r:id="rId29"/>
+    <sheet name="commonHW_DO" sheetId="28" state="visible" r:id="rId30"/>
+    <sheet name="commonHW_AI" sheetId="29" state="visible" r:id="rId31"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="298">
   <si>
     <t xml:space="preserve">POWER SUPPLY</t>
   </si>
@@ -363,6 +366,21 @@
   </si>
   <si>
     <t xml:space="preserve">1 x 12pin WEIDMÜLLER  B2CF 3.50/12/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x terminal DIN Molex 201606-0610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x terminal DIN WEIDMÜLLER WDU 1.5/R3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3x terminal DIN Molex 201606-6163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4x terminal DIN WEIDMÜLLER WDU 1.5/R3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO A, B</t>
   </si>
   <si>
     <t xml:space="preserve">425 A</t>
@@ -1395,7 +1413,7 @@
   <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -1412,7 +1430,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1420,7 +1438,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1428,7 +1446,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1436,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1444,7 +1462,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1452,7 +1470,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1508,7 +1526,7 @@
         <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1531,8 +1549,8 @@
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>32</v>
+      <c r="B20" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1548,7 +1566,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1556,44 +1574,55 @@
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>114</v>
+      <c r="B25" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>116</v>
+        <v>98</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1612,10 +1641,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -1632,7 +1661,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1640,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1648,7 +1677,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1656,143 +1685,143 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B21" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>113</v>
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1800,7 +1829,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1808,7 +1837,15 @@
         <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>105</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1827,10 +1864,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -1847,7 +1884,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1855,7 +1892,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1863,7 +1900,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1871,143 +1908,143 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>32</v>
+        <v>58</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>113</v>
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2024,6 +2061,22 @@
       </c>
       <c r="B28" s="1" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2042,237 +2095,208 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>83</v>
+      <c r="B2" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>128</v>
+      <c r="B3" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>129</v>
+      <c r="B4" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>130</v>
+      <c r="B5" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>131</v>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>57</v>
+      <c r="B7" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>1</v>
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>20</v>
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>1</v>
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>134</v>
+      <c r="B23" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>113</v>
+      <c r="A25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>135</v>
+      <c r="A26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+      <c r="A29" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>137</v>
+      <c r="A30" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2291,75 +2315,75 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>83</v>
+      <c r="B2" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>138</v>
+      <c r="B3" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>139</v>
+      <c r="B4" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
+      <c r="B5" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>133</v>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2370,158 +2394,124 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-    </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-    </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-    </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-    </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>134</v>
+      <c r="B24" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>113</v>
+      <c r="B25" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>135</v>
+      <c r="B26" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>115</v>
+      <c r="B27" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2540,75 +2530,75 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>83</v>
+      <c r="B2" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>142</v>
+      <c r="B3" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>143</v>
+      <c r="B4" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>144</v>
+      <c r="B5" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>133</v>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2619,158 +2609,124 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-    </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-    </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-    </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-    </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>134</v>
+      <c r="B24" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>113</v>
+      <c r="B25" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>135</v>
+      <c r="B26" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>115</v>
+      <c r="B27" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2817,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2825,7 +2781,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2833,7 +2789,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2841,7 +2797,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2849,15 +2805,15 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2969,7 +2925,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2977,7 +2933,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2985,7 +2941,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2993,7 +2949,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3010,16 +2966,16 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3038,75 +2994,75 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>152</v>
+      <c r="B2" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>153</v>
+      <c r="B3" s="3" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>154</v>
+      <c r="B4" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>149</v>
+      <c r="B5" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>155</v>
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>156</v>
+      <c r="A8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3117,145 +3073,158 @@
         <v>17</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+    </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+    </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>27</v>
       </c>
     </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+    </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="B23" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>157</v>
+      <c r="B24" s="3" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>158</v>
+      <c r="B25" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>51</v>
+      <c r="B26" s="3" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>159</v>
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>160</v>
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>161</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>162</v>
+      <c r="A31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3274,191 +3243,237 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>83</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>165</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>147</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>148</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>149</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>150</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>173</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>138</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="3"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>185</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>185</v>
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>193</v>
+      <c r="A23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3477,199 +3492,237 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>200</v>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="3"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>185</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>185</v>
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>193</v>
+      <c r="B25" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3911,12 +3964,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3932,130 +3984,111 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>163</v>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>158</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>165</v>
+      <c r="A4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>159</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>167</v>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>169</v>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>171</v>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>173</v>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>161</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>175</v>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>179</v>
+      <c r="A11" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>203</v>
+      <c r="A12" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>184</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>185</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>186</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4068,66 +4101,87 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>158</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>189</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>192</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>193</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>212</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -4146,7 +4200,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -4163,149 +4217,174 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>214</v>
+      <c r="A2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>216</v>
+      <c r="A3" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>214</v>
+      <c r="A4" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>219</v>
+      <c r="A7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>221</v>
+      <c r="A8" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>223</v>
+      <c r="A10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>225</v>
+      <c r="A11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>227</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>230</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>231</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>234</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -4324,7 +4403,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -4341,65 +4420,71 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>213</v>
+      <c r="A2" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>215</v>
+      <c r="A3" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>216</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>217</v>
+      <c r="A4" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
+      <c r="A6" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
+      <c r="A7" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>202</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
+      <c r="A8" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>204</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
+      <c r="A9" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -4407,85 +4492,110 @@
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>224</v>
+      <c r="A10" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C13" s="3"/>
-    </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
+      <c r="A14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>105</v>
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -4504,7 +4614,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -4522,102 +4632,110 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>228</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>235</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
@@ -4626,22 +4744,93 @@
       <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>100</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -4656,6 +4845,520 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4676,107 +5379,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4784,16 +5487,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2.05</v>
@@ -4819,16 +5522,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2.05</v>
@@ -4854,16 +5557,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2.05</v>
@@ -4889,16 +5592,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2.05</v>
@@ -4924,16 +5627,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2.05</v>
@@ -4959,16 +5662,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2.05</v>
@@ -4994,16 +5697,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1.25</v>
@@ -5029,16 +5732,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1.25</v>
@@ -5070,7 +5773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5090,89 +5793,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5192,7 +5895,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>300</v>
@@ -5221,7 +5924,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>300</v>
@@ -5250,7 +5953,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>300</v>
@@ -5279,7 +5982,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>300</v>
@@ -5308,7 +6011,7 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>300</v>
@@ -5337,7 +6040,7 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>300</v>
@@ -5360,7 +6063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5376,44 +6079,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5421,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>11</v>
@@ -5435,7 +6138,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>11</v>
@@ -6634,10 +7337,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -6686,7 +7389,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6750,7 +7453,7 @@
         <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6773,8 +7476,8 @@
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>32</v>
+      <c r="B20" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6790,7 +7493,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6798,7 +7501,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6806,7 +7509,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6814,7 +7517,7 @@
         <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6822,7 +7525,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6830,7 +7533,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6838,7 +7541,15 @@
         <v>98</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>94</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -6909,7 +7620,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Manual/source/tab/parametersEN.xlsx
+++ b/Manual/source/tab/parametersEN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,15 +28,18 @@
     <sheet name="TGZ-S-400-10_20" sheetId="18" state="visible" r:id="rId20"/>
     <sheet name="TGZ-S-400-14_30" sheetId="19" state="visible" r:id="rId21"/>
     <sheet name="TGZ-D-560-30_50" sheetId="20" state="visible" r:id="rId22"/>
-    <sheet name="TGS-320-10_15" sheetId="21" state="visible" r:id="rId23"/>
-    <sheet name="TGS-560-25_50" sheetId="22" state="visible" r:id="rId24"/>
-    <sheet name="TGS-560-50_100" sheetId="23" state="visible" r:id="rId25"/>
-    <sheet name="TGMmini" sheetId="24" state="visible" r:id="rId26"/>
-    <sheet name="TGMcontroller" sheetId="25" state="visible" r:id="rId27"/>
-    <sheet name="TGZpMotion" sheetId="26" state="visible" r:id="rId28"/>
-    <sheet name="commonHW_DI" sheetId="27" state="visible" r:id="rId29"/>
-    <sheet name="commonHW_DO" sheetId="28" state="visible" r:id="rId30"/>
-    <sheet name="commonHW_AI" sheetId="29" state="visible" r:id="rId31"/>
+    <sheet name="TGZ-D-560-3_9" sheetId="21" state="visible" r:id="rId23"/>
+    <sheet name="TGZ-D-560-7_15" sheetId="22" state="visible" r:id="rId24"/>
+    <sheet name="TGZ-D-560-10_20" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="TGS-320-10_15" sheetId="24" state="visible" r:id="rId26"/>
+    <sheet name="TGS-560-25_50" sheetId="25" state="visible" r:id="rId27"/>
+    <sheet name="TGS-560-50_100" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="TGMmini" sheetId="27" state="visible" r:id="rId29"/>
+    <sheet name="TGMcontroller" sheetId="28" state="visible" r:id="rId30"/>
+    <sheet name="TGZpMotion" sheetId="29" state="visible" r:id="rId31"/>
+    <sheet name="commonHW_DI" sheetId="30" state="visible" r:id="rId32"/>
+    <sheet name="commonHW_DO" sheetId="31" state="visible" r:id="rId33"/>
+    <sheet name="commonHW_AI" sheetId="32" state="visible" r:id="rId34"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -48,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="298">
   <si>
     <t xml:space="preserve">POWER SUPPLY</t>
   </si>
@@ -4200,12 +4203,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4217,174 +4219,208 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="3"/>
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C3" s="3"/>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="3"/>
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C5" s="3"/>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="3"/>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="3"/>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C8" s="3"/>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C10" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C11" s="3"/>
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>188</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>190</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>192</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>193</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>195</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>196</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>197</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>198</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -4403,12 +4439,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4420,163 +4455,144 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>168</v>
+      <c r="A2" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>157</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>170</v>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>158</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>172</v>
+      <c r="A4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>159</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>174</v>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>176</v>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>178</v>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>203</v>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>161</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>205</v>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>208</v>
+      <c r="A11" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>188</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>190</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>192</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>193</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>210</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>1</v>
@@ -4584,18 +4600,63 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>198</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -4614,12 +4675,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4639,126 +4699,107 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>168</v>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>158</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>170</v>
+      <c r="A4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>159</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>172</v>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>174</v>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>176</v>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>178</v>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>161</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>180</v>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>184</v>
+      <c r="A11" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>208</v>
+      <c r="A12" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>189</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>190</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>191</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4771,66 +4812,87 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>163</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>198</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>215</v>
+        <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>216</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>217</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -4849,7 +4911,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -4866,149 +4928,174 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>219</v>
+      <c r="A2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>221</v>
+      <c r="A3" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>219</v>
+      <c r="A4" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>224</v>
+      <c r="A7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>226</v>
+      <c r="A8" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>228</v>
+      <c r="A10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>230</v>
+      <c r="A11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>231</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>235</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>236</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>239</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -5027,7 +5114,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -5044,65 +5131,71 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>218</v>
+      <c r="A2" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>220</v>
+      <c r="A3" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>222</v>
+      <c r="A4" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
+      <c r="A6" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
+      <c r="A7" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>202</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
+      <c r="A8" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>204</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
+      <c r="A9" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -5110,85 +5203,110 @@
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>229</v>
+      <c r="A10" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C13" s="3"/>
-    </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
+      <c r="A14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>235</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>105</v>
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -5207,7 +5325,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -5225,126 +5343,205 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>218</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>157</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>220</v>
+      <c r="A3" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>222</v>
+      <c r="A4" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>200</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
+      <c r="A6" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
+      <c r="A7" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
+      <c r="A8" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
+      <c r="A9" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>229</v>
+      <c r="A10" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
+      <c r="A12" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>100</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -5363,403 +5560,166 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="26.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>251</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>262</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>269</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
+      <c r="A4" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>50</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>50</v>
-      </c>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>3</v>
+      <c r="A6" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>4</v>
+      <c r="A7" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>50</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>5</v>
+      <c r="A8" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>50</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>6</v>
+      <c r="A9" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>7</v>
+      <c r="A10" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>50</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>8</v>
+      <c r="A11" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>50</v>
+        <v>230</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -5778,278 +5738,168 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="26.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>282</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>289</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>269</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="n">
+      <c r="A4" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>10</v>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -6068,83 +5918,144 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>296</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>297</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
+      <c r="A4" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>22</v>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -6373,6 +6284,806 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="26.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="26.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30.24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/Manual/source/tab/parametersEN.xlsx
+++ b/Manual/source/tab/parametersEN.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="308">
   <si>
     <t xml:space="preserve">POWER SUPPLY</t>
   </si>
@@ -557,6 +557,45 @@
     <t xml:space="preserve">Filter already inside of TGS-560</t>
   </si>
   <si>
+    <t xml:space="preserve">140-600 VDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,4 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 9 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 3pin WEIDMÜLLER BLZ 7.62HP/03/180LR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin WEIDMÜLLER BCZ 3.81/05/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 6pin WEIDMÜLLER  BLZ 7.62HP/06/180LR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter already inside of TGS-560-25/50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 20 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 W</t>
+  </si>
+  <si>
     <t xml:space="preserve">Input voltage (VAC - 50/60 Hz) </t>
   </si>
   <si>
@@ -566,9 +605,6 @@
     <t xml:space="preserve">Maximum input current (AC) </t>
   </si>
   <si>
-    <t xml:space="preserve">16 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">Output voltage (DC) </t>
   </si>
   <si>
@@ -683,13 +719,7 @@
     <t xml:space="preserve">32 A</t>
   </si>
   <si>
-    <t xml:space="preserve">1 x 5pin WEIDMÜLLER BCZ 3.81/05/180F</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 x 400 VAC/50Hz 63A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 W</t>
   </si>
   <si>
     <t xml:space="preserve">63 A</t>
@@ -4203,7 +4233,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -4231,7 +4261,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4239,7 +4269,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4247,7 +4277,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4255,7 +4285,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4263,7 +4293,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4271,7 +4301,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4367,7 +4397,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4375,7 +4405,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4383,44 +4413,36 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="1" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>167</v>
+      <c r="B31" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -4439,8 +4461,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
@@ -4467,7 +4489,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4475,7 +4497,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4483,7 +4505,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4491,7 +4513,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4499,7 +4521,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4507,7 +4529,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4603,7 +4625,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4611,7 +4633,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4619,44 +4641,36 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="1" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>167</v>
+      <c r="B31" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -4675,8 +4689,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
@@ -4703,7 +4717,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4711,7 +4725,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4719,7 +4733,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4727,7 +4741,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4735,7 +4749,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4743,7 +4757,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4839,7 +4853,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4847,7 +4861,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4855,44 +4869,36 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="1" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>167</v>
+      <c r="B31" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -4929,91 +4935,91 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -5028,7 +5034,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -5036,18 +5042,18 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5063,12 +5069,12 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1</v>
@@ -5076,7 +5082,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>130</v>
@@ -5084,18 +5090,18 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -5132,16 +5138,16 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -5150,25 +5156,25 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>46</v>
@@ -5177,25 +5183,25 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -5204,19 +5210,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -5231,7 +5237,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -5239,18 +5245,18 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5266,12 +5272,12 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1</v>
@@ -5282,12 +5288,12 @@
         <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>210</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>1</v>
@@ -5295,7 +5301,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>1</v>
@@ -5303,10 +5309,10 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -5351,16 +5357,16 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>46</v>
@@ -5369,16 +5375,16 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>46</v>
@@ -5387,7 +5393,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>56</v>
@@ -5396,7 +5402,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>159</v>
@@ -5405,16 +5411,16 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
@@ -5423,19 +5429,19 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -5450,7 +5456,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -5458,18 +5464,18 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5485,12 +5491,12 @@
         <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>1</v>
@@ -5506,15 +5512,15 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>162</v>
@@ -5522,26 +5528,26 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -5578,28 +5584,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5617,19 +5623,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -5644,28 +5650,28 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -5683,16 +5689,16 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1</v>
@@ -5700,10 +5706,10 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5711,15 +5717,15 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -5756,28 +5762,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5822,10 +5828,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -5843,10 +5849,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -5855,7 +5861,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -5864,7 +5870,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>37</v>
@@ -5875,7 +5881,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5936,28 +5942,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -6002,10 +6008,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -6023,10 +6029,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -6035,7 +6041,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -6047,7 +6053,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6305,107 +6311,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6413,16 +6419,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2.05</v>
@@ -6448,16 +6454,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2.05</v>
@@ -6483,16 +6489,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2.05</v>
@@ -6518,16 +6524,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2.05</v>
@@ -6553,16 +6559,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2.05</v>
@@ -6588,16 +6594,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2.05</v>
@@ -6623,16 +6629,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1.25</v>
@@ -6658,16 +6664,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1.25</v>
@@ -6719,89 +6725,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6821,7 +6827,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>300</v>
@@ -6850,7 +6856,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>300</v>
@@ -6879,7 +6885,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>300</v>
@@ -6908,7 +6914,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>300</v>
@@ -6937,7 +6943,7 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>300</v>
@@ -6966,7 +6972,7 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>300</v>
@@ -7005,44 +7011,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7050,7 +7056,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>11</v>
@@ -7064,7 +7070,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>11</v>

--- a/Manual/source/tab/parametersEN.xlsx
+++ b/Manual/source/tab/parametersEN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="316">
   <si>
     <t xml:space="preserve">POWER SUPPLY</t>
   </si>
@@ -689,6 +689,9 @@
     <t xml:space="preserve">3 x 400 VAC</t>
   </si>
   <si>
+    <t xml:space="preserve">32 A</t>
+  </si>
+  <si>
     <t xml:space="preserve">560 VDC</t>
   </si>
   <si>
@@ -707,19 +710,40 @@
     <t xml:space="preserve">Maximum braking power (external resistor)</t>
   </si>
   <si>
+    <t xml:space="preserve">9 kW</t>
+  </si>
+  <si>
     <t xml:space="preserve">Losses at maximum output power</t>
   </si>
   <si>
     <t xml:space="preserve">100 W</t>
   </si>
   <si>
+    <t xml:space="preserve">Recommended circuit breaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC IN connector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin WEIDMÜLLER BVF 7.62HP/04/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 6pin WEIDMÜLLER BVF 7.62HP/06/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin WEIDMÜLLER BCZ 3.81/04/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brake resistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 3pin WEIDMÜLLER BLZ 7.62HP/03/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x 400 VAC/50Hz 63A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fuse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 x 400 VAC/50Hz 63A</t>
   </si>
   <si>
     <t xml:space="preserve">63 A</t>
@@ -5120,7 +5144,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -5150,7 +5174,7 @@
         <v>183</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>212</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -5159,7 +5183,7 @@
         <v>184</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5168,7 +5192,7 @@
         <v>186</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -5186,43 +5210,43 @@
         <v>190</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>219</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -5293,10 +5317,10 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5304,7 +5328,7 @@
         <v>207</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5312,7 +5336,15 @@
         <v>209</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>210</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -5360,7 +5392,7 @@
         <v>181</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -5378,7 +5410,7 @@
         <v>184</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -5414,7 +5446,7 @@
         <v>192</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -5438,10 +5470,10 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -5515,7 +5547,7 @@
         <v>206</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5536,7 +5568,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>210</v>
@@ -5544,10 +5576,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -5584,28 +5616,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5623,19 +5655,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -5650,28 +5682,28 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -5689,10 +5721,10 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C15" s="3"/>
     </row>
@@ -5706,10 +5738,10 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5717,15 +5749,15 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -5762,28 +5794,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5828,10 +5860,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -5849,10 +5881,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -5870,7 +5902,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>37</v>
@@ -5881,7 +5913,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5942,28 +5974,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -6008,10 +6040,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -6029,10 +6061,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -6053,7 +6085,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6311,107 +6343,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6419,16 +6451,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2.05</v>
@@ -6454,16 +6486,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2.05</v>
@@ -6489,16 +6521,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2.05</v>
@@ -6524,16 +6556,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2.05</v>
@@ -6559,16 +6591,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2.05</v>
@@ -6594,16 +6626,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2.05</v>
@@ -6629,16 +6661,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1.25</v>
@@ -6664,16 +6696,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1.25</v>
@@ -6725,89 +6757,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6827,7 +6859,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>300</v>
@@ -6856,7 +6888,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>300</v>
@@ -6885,7 +6917,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>300</v>
@@ -6914,7 +6946,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>300</v>
@@ -6943,7 +6975,7 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>300</v>
@@ -6972,7 +7004,7 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>300</v>
@@ -7011,44 +7043,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7056,7 +7088,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>11</v>
@@ -7070,7 +7102,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>11</v>
